--- a/polls/004_public_opinion_poll_questionnaire--polls.xlsx
+++ b/polls/004_public_opinion_poll_questionnaire--polls.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'red'}</t>
+          <t>red</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'green'}</t>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'summer'}</t>
+          <t>summer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'summer'}</t>
+          <t>summer</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'winter'}</t>
+          <t>winter</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'winter'}</t>
+          <t>winter</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'spring'}</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'spring'}</t>
+          <t>spring</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'autumn'}</t>
+          <t>autumn</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'autumn'}</t>
+          <t>autumn</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_a_month'}</t>
+          <t>less_than_a_month</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'less than a month'}</t>
+          <t>less than a month</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'more_than_a_month_but_less_than_a_year'}</t>
+          <t>more_than_a_month_but_less_than_a_year</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'more than a month but less than a year'}</t>
+          <t>more than a month but less than a year</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'more_than_a_year'}</t>
+          <t>more_than_a_year</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'more than a year'}</t>
+          <t>more than a year</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'classical'}</t>
+          <t>classical</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'classical'}</t>
+          <t>classical</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'pop'}</t>
+          <t>pop</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'pop'}</t>
+          <t>pop</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rock'}</t>
+          <t>rock</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'rock'}</t>
+          <t>rock</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'jazz'}</t>
+          <t>jazz</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'jazz'}</t>
+          <t>jazz</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'basketball'}</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'basketball'}</t>
+          <t>basketball</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'soccer'}</t>
+          <t>soccer</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'soccer'}</t>
+          <t>soccer</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'tennis'}</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'tennis'}</t>
+          <t>tennis</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'volleyball'}</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'volleyball'}</t>
+          <t>volleyball</t>
         </is>
       </c>
     </row>
@@ -1449,12 +1449,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'red'}</t>
+          <t>red</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1483,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'green'}</t>
+          <t>green</t>
         </is>
       </c>
     </row>
